--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:59</t>
+    <t xml:space="preserve">2026-09-09 22:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:50</t>
+    <t xml:space="preserve">2026-09-18 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:12</t>
+    <t xml:space="preserve">2026-09-23 12:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -657,7 +657,9 @@
       <c r="C11" s="2" t="n">
         <v>11302</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="n">
+        <v>2023</v>
+      </c>
       <c r="E11" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:16</t>
+    <t xml:space="preserve">2026-10-02 13:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:51</t>
+    <t xml:space="preserve">2026-10-04 08:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:36</t>
+    <t xml:space="preserve">2026-10-05 09:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
